--- a/02_Zero_Shot/outputs/Embedding/all-mpnet-base-v2/RESULT_pan_all-mpnet-base-v2_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/Embedding/all-mpnet-base-v2/RESULT_pan_all-mpnet-base-v2_zeroshot.xlsx
@@ -24119,7 +24119,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4612572611486563</v>
+        <v>0.4612572611486562</v>
       </c>
     </row>
     <row r="4">
@@ -24159,7 +24159,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.501957800000127</v>
+        <v>22.17171129200142</v>
       </c>
     </row>
     <row r="8">
@@ -24169,7 +24169,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.005397091942446135</v>
+        <v>0.01595087143309454</v>
       </c>
     </row>
   </sheetData>
